--- a/fixtures/cp-068-prepship-invoice-workbook.xlsx
+++ b/fixtures/cp-068-prepship-invoice-workbook.xlsx
@@ -94,7 +94,7 @@
     <t>Widget A</t>
   </si>
   <si>
-    <t>9002 - Return</t>
+    <t>9002-RETURN</t>
   </si>
   <si>
     <t>SKU-B</t>
